--- a/data/fmsForecastOutput/File1/RPT_RPT4905554084177SD_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4905554084177SD_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>408.7333657886404</v>
+        <v>408.7333657886402</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>438.7252650738636</v>
+        <v>438.7252650738633</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>468.9540363164137</v>
+        <v>468.9540363164135</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>528.9829036753312</v>
+        <v>528.982903675331</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>564.8457039941435</v>
+        <v>564.8457039941432</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>408.7333657886404</v>
+        <v>408.7333657886402</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>438.7252650738636</v>
+        <v>438.7252650738633</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>468.9540363164137</v>
+        <v>468.9540363164135</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>528.9829036753312</v>
+        <v>528.982903675331</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>564.8457039941435</v>
+        <v>564.8457039941432</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>5653846.894268111</v>
+        <v>5653846.894268109</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>6700023.824717863</v>
+        <v>6700023.824717861</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>7819019.014773175</v>
+        <v>7819019.014773171</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>9026386.940271594</v>
+        <v>9026386.940271592</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>10565110.98315269</v>
+        <v>10565110.98315268</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>407.6883366639186</v>
+        <v>407.6883366639184</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>437.6035541539125</v>
+        <v>437.6035541539123</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>467.7550379788034</v>
+        <v>467.7550379788032</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>527.6304265176273</v>
+        <v>527.630426517627</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>563.4015346136748</v>
+        <v>563.4015346136746</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>407.6883366639186</v>
+        <v>407.6883366639184</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>437.6035541539125</v>
+        <v>437.6035541539123</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>467.7550379788034</v>
+        <v>467.7550379788032</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>527.6304265176273</v>
+        <v>527.630426517627</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>563.4015346136748</v>
+        <v>563.4015346136746</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>5653846.894268111</v>
+        <v>5653846.894268109</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>6700023.824717863</v>
+        <v>6700023.824717861</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>7819019.014773175</v>
+        <v>7819019.014773171</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>9026386.940271594</v>
+        <v>9026386.940271592</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>10565110.98315269</v>
+        <v>10565110.98315268</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>811.3066839943605</v>
+        <v>811.3066839943602</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>889.2369166108344</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>959.7244895281034</v>
+        <v>959.724489528103</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>1217.459514609757</v>
@@ -2037,13 +2037,13 @@
         <v>1296.757453016447</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>811.3066839943605</v>
+        <v>811.3066839943602</v>
       </c>
       <c r="I9" s="156" t="n">
         <v>889.2369166108344</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>959.7244895281034</v>
+        <v>959.724489528103</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>1217.459514609757</v>
@@ -2058,7 +2058,7 @@
         <v>2719454.98440542</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>3159722.739748795</v>
+        <v>3159722.739748794</v>
       </c>
       <c r="P9" s="159" t="n">
         <v>3533805.388202056</v>
@@ -2108,7 +2108,7 @@
         <v>2719454.98440542</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>3159722.739748795</v>
+        <v>3159722.739748794</v>
       </c>
       <c r="AG9" s="159" t="n">
         <v>3533805.388202056</v>
@@ -2170,40 +2170,40 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>477.4497012577662</v>
+        <v>477.449701257766</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>513.8899150007749</v>
+        <v>513.8899150007746</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>549.8818095026068</v>
+        <v>549.8818095026065</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>629.0705169702811</v>
+        <v>629.0705169702809</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>671.4973433596717</v>
+        <v>671.4973433596716</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>477.4497012577662</v>
+        <v>477.449701257766</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>513.8899150007749</v>
+        <v>513.8899150007746</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>549.8818095026068</v>
+        <v>549.8818095026065</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>629.0705169702811</v>
+        <v>629.0705169702809</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>671.4973433596717</v>
+        <v>671.4973433596716</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>7963722.185236844</v>
+        <v>7963722.185236841</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>9419478.809123283</v>
+        <v>9419478.80912328</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>10978741.75452197</v>
@@ -2220,40 +2220,40 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>492.4577161038538</v>
+        <v>492.4577161038536</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>529.6363031743601</v>
+        <v>529.6363031743599</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>566.5114141868006</v>
+        <v>566.5114141868004</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>645.5815037791496</v>
+        <v>645.5815037791493</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>689.1685807488753</v>
+        <v>689.1685807488751</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>492.4577161038538</v>
+        <v>492.4577161038536</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>529.6363031743601</v>
+        <v>529.6363031743599</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>566.5114141868006</v>
+        <v>566.5114141868004</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>645.5815037791496</v>
+        <v>645.5815037791493</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>689.1685807488753</v>
+        <v>689.1685807488751</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>7963722.185236844</v>
+        <v>7963722.185236841</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>9419478.809123283</v>
+        <v>9419478.80912328</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>10978741.75452197</v>
@@ -2348,7 +2348,7 @@
         <v>1481.23691407599</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>88486.56353944131</v>
+        <v>88486.56353944133</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>106408.2226361601</v>
@@ -2374,7 +2374,7 @@
         <v>1252.701998198001</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1333.94487908572</v>
+        <v>1333.944879085721</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1439.830176496273</v>
@@ -2389,7 +2389,7 @@
         <v>1252.701998198001</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1333.94487908572</v>
+        <v>1333.944879085721</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>1439.830176496273</v>
@@ -2398,7 +2398,7 @@
         <v>1520.256199895363</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>88486.56353944131</v>
+        <v>88486.56353944133</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>106408.2226361601</v>
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>480.472525983425</v>
+        <v>480.4725259834247</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>517.2350422580162</v>
+        <v>517.2350422580161</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>553.5622532641053</v>
+        <v>553.562253264105</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>633.2523020939333</v>
+        <v>633.2523020939331</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>676.0732158478488</v>
+        <v>676.0732158478486</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>480.472525983425</v>
+        <v>480.4725259834247</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>517.2350422580162</v>
+        <v>517.2350422580161</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>553.5622532641053</v>
+        <v>553.562253264105</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>633.2523020939333</v>
+        <v>633.2523020939331</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>676.0732158478488</v>
+        <v>676.0732158478486</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>8052208.748776284</v>
+        <v>8052208.748776281</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>9525887.031759443</v>
+        <v>9525887.031759441</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>11106740.48107405</v>
+        <v>11106740.48107404</v>
       </c>
       <c r="P12" s="165" t="n">
         <v>12712387.10524857</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>14886655.47971147</v>
+        <v>14886655.47971146</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>495.5639377064616</v>
+        <v>495.5639377064614</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>533.0733601315441</v>
+        <v>533.0733601315437</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>570.292526292207</v>
+        <v>570.2925262922068</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>649.8733742773422</v>
+        <v>649.873374277342</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>693.8649727564574</v>
+        <v>693.8649727564572</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>495.5639377064616</v>
+        <v>495.5639377064614</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>533.0733601315441</v>
+        <v>533.0733601315437</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>570.292526292207</v>
+        <v>570.2925262922068</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>649.8733742773422</v>
+        <v>649.873374277342</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>693.8649727564574</v>
+        <v>693.8649727564572</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>8052208.748776284</v>
+        <v>8052208.748776281</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>9525887.031759443</v>
+        <v>9525887.031759441</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>11106740.48107405</v>
+        <v>11106740.48107404</v>
       </c>
       <c r="AG12" s="165" t="n">
         <v>12712387.10524857</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>14886655.47971147</v>
+        <v>14886655.47971146</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>2376.235616754715</v>
+        <v>2376.235616754714</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>2446.52503057958</v>
+        <v>2446.525030579579</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>2560.317278211295</v>
+        <v>2560.317278211294</v>
       </c>
       <c r="F13" s="156" t="n">
         <v>2674.357244279411</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>2824.018930082077</v>
+        <v>2824.018930082076</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2376.235616754715</v>
+        <v>2376.235616754714</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2446.52503057958</v>
+        <v>2446.525030579579</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>2560.317278211295</v>
+        <v>2560.317278211294</v>
       </c>
       <c r="K13" s="156" t="n">
         <v>2674.357244279411</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>2824.018930082077</v>
+        <v>2824.018930082076</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>3032545.776071096</v>
+        <v>3032545.776071095</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>3546675.706107755</v>
+        <v>3546675.706107754</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>4175328.357466702</v>
+        <v>4175328.357466701</v>
       </c>
       <c r="P13" s="159" t="n">
         <v>4921460.686222831</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>5899936.188174443</v>
+        <v>5899936.188174441</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         <v>1301.044510002928</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>1361.558413278655</v>
+        <v>1361.558413278654</v>
       </c>
       <c r="W13" s="156" t="n">
         <v>1422.204051446801</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>1501.793065349191</v>
+        <v>1501.79306534919</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>1263.665102547407</v>
@@ -2674,28 +2674,28 @@
         <v>1301.044510002928</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>1361.558413278655</v>
+        <v>1361.558413278654</v>
       </c>
       <c r="AB13" s="156" t="n">
         <v>1422.204051446801</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>1501.793065349191</v>
+        <v>1501.79306534919</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>3032545.776071096</v>
+        <v>3032545.776071095</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>3546675.706107755</v>
+        <v>3546675.706107754</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>4175328.357466702</v>
+        <v>4175328.357466701</v>
       </c>
       <c r="AG13" s="159" t="n">
         <v>4921460.686222831</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>5899936.188174443</v>
+        <v>5899936.188174441</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,34 +2746,34 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>614.6200144808216</v>
+        <v>614.6200144808212</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>658.0164664086301</v>
+        <v>658.0164664086299</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>704.4081175181863</v>
+        <v>704.4081175181861</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>804.6474311393007</v>
+        <v>804.6474311393008</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>862.2103149857608</v>
+        <v>862.2103149857605</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>614.6200144808216</v>
+        <v>614.6200144808212</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>658.0164664086301</v>
+        <v>658.0164664086299</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>704.4081175181863</v>
+        <v>704.4081175181861</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>804.6474311393007</v>
+        <v>804.6474311393008</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>862.2103149857608</v>
+        <v>862.2103149857605</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>11084754.52484738</v>
@@ -2782,13 +2782,13 @@
         <v>13072562.7378672</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>15282068.83854075</v>
+        <v>15282068.83854074</v>
       </c>
       <c r="P14" s="171" t="n">
         <v>17633847.7914714</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>20786591.66788591</v>
+        <v>20786591.6678859</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,34 +2796,34 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>594.4084850984217</v>
+        <v>594.4084850984212</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>634.7207392329732</v>
+        <v>634.7207392329731</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>677.9347155403568</v>
+        <v>677.9347155403567</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>765.9638465032506</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>818.908774393677</v>
+        <v>818.9087743936768</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>594.4084850984217</v>
+        <v>594.4084850984212</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>634.7207392329732</v>
+        <v>634.7207392329731</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>677.9347155403568</v>
+        <v>677.9347155403567</v>
       </c>
       <c r="AB14" s="168" t="n">
         <v>765.9638465032506</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>818.908774393677</v>
+        <v>818.9087743936768</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>11084754.52484738</v>
@@ -2832,13 +2832,13 @@
         <v>13072562.7378672</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>15282068.83854075</v>
+        <v>15282068.83854074</v>
       </c>
       <c r="AG14" s="171" t="n">
         <v>17633847.7914714</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>20786591.66788591</v>
+        <v>20786591.6678859</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>79.22768530347238</v>
+        <v>79.22768530347237</v>
       </c>
       <c r="D22" s="80" t="n">
         <v>87.18056425528344</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="79" t="n">
-        <v>79.22768530347238</v>
+        <v>79.22768530347237</v>
       </c>
       <c r="N22" s="80" t="n">
         <v>87.18056425528344</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>77.19420719769241</v>
+        <v>77.19420719769239</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>84.94296551711996</v>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="79" t="n">
-        <v>77.19420719769241</v>
+        <v>77.19420719769239</v>
       </c>
       <c r="AE22" s="80" t="n">
         <v>84.94296551711996</v>
@@ -3756,7 +3756,7 @@
         <v>16248.5768961378</v>
       </c>
       <c r="U23" s="86" t="n">
-        <v>17869.74878918876</v>
+        <v>17869.74878918877</v>
       </c>
       <c r="V23" s="86" t="n">
         <v>19475.51470345442</v>
@@ -3786,7 +3786,7 @@
         <v>16248.5768961378</v>
       </c>
       <c r="AE23" s="86" t="n">
-        <v>17869.74878918876</v>
+        <v>17869.74878918877</v>
       </c>
       <c r="AF23" s="86" t="n">
         <v>19475.51470345442</v>
@@ -3846,7 +3846,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="E24" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="F24" s="80" t="n">
         <v>1840.240564999343</v>
@@ -3876,7 +3876,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="O24" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="P24" s="80" t="n">
         <v>1840.240564999343</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>18648.37868694283</v>
+        <v>18648.37868694284</v>
       </c>
       <c r="U25" s="92" t="n">
         <v>20595.77059615967</v>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>18648.37868694283</v>
+        <v>18648.37868694284</v>
       </c>
       <c r="AE25" s="92" t="n">
         <v>20595.77059615967</v>
@@ -4408,46 +4408,46 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>418.1341945292035</v>
+        <v>418.1341945292032</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>459.1471193707464</v>
+        <v>459.1471193707462</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>493.7619694202502</v>
+        <v>493.76196942025</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>566.4267270951322</v>
+        <v>566.4267270951319</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>606.5304764977104</v>
+        <v>606.5304764977101</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>418.1341945292035</v>
+        <v>418.1341945292032</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>459.1471193707464</v>
+        <v>459.1471193707462</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>493.7619694202502</v>
+        <v>493.76196942025</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>566.4267270951322</v>
+        <v>566.4267270951319</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>606.5304764977104</v>
+        <v>606.5304764977101</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>5783884.837893844</v>
+        <v>5783884.837893841</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>7011897.612772891</v>
+        <v>7011897.612772889</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>8232649.532125711</v>
+        <v>8232649.532125708</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>9665315.791019043</v>
+        <v>9665315.791019039</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>11344800.45355755</v>
@@ -4458,46 +4458,46 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>417.0651298334892</v>
+        <v>417.065129833489</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>457.973194870238</v>
+        <v>457.9731948702379</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>492.4995433941085</v>
+        <v>492.4995433941082</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>564.9785154334952</v>
+        <v>564.978515433495</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>604.979729565787</v>
+        <v>604.9797295657867</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>417.0651298334892</v>
+        <v>417.065129833489</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>457.973194870238</v>
+        <v>457.9731948702379</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>492.4995433941085</v>
+        <v>492.4995433941082</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>564.9785154334952</v>
+        <v>564.978515433495</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>604.979729565787</v>
+        <v>604.9797295657867</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>5783884.837893844</v>
+        <v>5783884.837893841</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>7011897.612772891</v>
+        <v>7011897.612772889</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>8232649.532125711</v>
+        <v>8232649.532125708</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>9665315.791019043</v>
+        <v>9665315.791019039</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>11344800.45355755</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>824.8537073146637</v>
+        <v>824.8537073146634</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>923.3947374090013</v>
@@ -4525,7 +4525,7 @@
         <v>1392.447379179805</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>824.8537073146637</v>
+        <v>824.8537073146634</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>923.3947374090013</v>
@@ -4540,13 +4540,13 @@
         <v>1392.447379179805</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>2348445.088372205</v>
+        <v>2348445.088372204</v>
       </c>
       <c r="N36" s="159" t="n">
         <v>2823916.072660772</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>3296723.532102585</v>
+        <v>3296723.532102584</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>3784978.336191925</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1019.590763576838</v>
+        <v>1019.590763576837</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>1141.39602822749</v>
@@ -4575,7 +4575,7 @@
         <v>1721.185798146518</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1019.590763576838</v>
+        <v>1019.590763576837</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>1141.39602822749</v>
@@ -4590,13 +4590,13 @@
         <v>1721.185798146518</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>2348445.088372205</v>
+        <v>2348445.088372204</v>
       </c>
       <c r="AE36" s="159" t="n">
         <v>2823916.072660772</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>3296723.532102585</v>
+        <v>3296723.532102584</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>3784978.336191925</v>
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>487.5582552368809</v>
+        <v>487.5582552368808</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>536.603517158017</v>
+        <v>536.6035171580168</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>577.4607568647117</v>
+        <v>577.4607568647115</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>673.6507896320696</v>
+        <v>673.6507896320695</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>721.0515593852177</v>
+        <v>721.0515593852176</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>487.5582552368809</v>
+        <v>487.5582552368808</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>536.603517158017</v>
+        <v>536.6035171580168</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>577.4607568647117</v>
+        <v>577.4607568647115</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>673.6507896320696</v>
+        <v>673.6507896320695</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>721.0515593852177</v>
+        <v>721.0515593852176</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>8132329.926266048</v>
+        <v>8132329.926266045</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>9835813.685433663</v>
+        <v>9835813.68543366</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>11529373.0642283</v>
+        <v>11529373.06422829</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>13450294.12721097</v>
+        <v>13450294.12721096</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>15787325.02587534</v>
+        <v>15787325.02587533</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>502.8840194245042</v>
+        <v>502.884019424504</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>553.0458855132484</v>
+        <v>553.0458855132482</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>594.9244080372825</v>
+        <v>594.9244080372823</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>691.3318587671606</v>
+        <v>691.3318587671604</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>740.0268738846032</v>
+        <v>740.026873884603</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>502.8840194245042</v>
+        <v>502.884019424504</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>553.0458855132484</v>
+        <v>553.0458855132482</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>594.9244080372825</v>
+        <v>594.9244080372823</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>691.3318587671606</v>
+        <v>691.3318587671604</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>740.0268738846032</v>
+        <v>740.026873884603</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>8132329.926266048</v>
+        <v>8132329.926266045</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>9835813.685433663</v>
+        <v>9835813.68543366</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>11529373.0642283</v>
+        <v>11529373.06422829</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>13450294.12721097</v>
+        <v>13450294.12721096</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>15787325.02587534</v>
+        <v>15787325.02587533</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4744,7 +4744,7 @@
         <v>1585.577104851202</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>90493.06961541572</v>
+        <v>90493.06961541573</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>111344.0345505115</v>
@@ -4756,7 +4756,7 @@
         <v>162508.4636991528</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>197296.4740111041</v>
+        <v>197296.474011104</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>1627.344958227605</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>90493.06961541572</v>
+        <v>90493.06961541573</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>111344.0345505115</v>
@@ -4806,7 +4806,7 @@
         <v>162508.4636991528</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>197296.4740111041</v>
+        <v>197296.474011104</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,43 +4816,43 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>490.6530194148507</v>
+        <v>490.6530194148505</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>540.1091285766462</v>
+        <v>540.109128576646</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>581.341268101722</v>
+        <v>581.3412681017218</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>678.1054185397649</v>
+        <v>678.1054185397646</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>725.9370297288796</v>
+        <v>725.9370297288793</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>490.6530194148507</v>
+        <v>490.6530194148505</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>540.1091285766462</v>
+        <v>540.109128576646</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>581.341268101722</v>
+        <v>581.3412681017218</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>678.1054185397649</v>
+        <v>678.1054185397646</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>725.9370297288796</v>
+        <v>725.9370297288793</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>8222822.995881463</v>
+        <v>8222822.995881461</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>9947157.719984176</v>
+        <v>9947157.719984172</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>11664102.01864643</v>
+        <v>11664102.01864642</v>
       </c>
       <c r="P39" s="165" t="n">
         <v>13612802.59091012</v>
@@ -4866,43 +4866,43 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>506.0641955564727</v>
+        <v>506.0641955564725</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>556.6478766619387</v>
+        <v>556.6478766619383</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>598.9111043405459</v>
+        <v>598.9111043405458</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>695.9037574834081</v>
+        <v>695.9037574834078</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>745.0410185589892</v>
+        <v>745.041018558989</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>506.0641955564727</v>
+        <v>506.0641955564725</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>556.6478766619387</v>
+        <v>556.6478766619383</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>598.9111043405459</v>
+        <v>598.9111043405458</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>695.9037574834081</v>
+        <v>695.9037574834078</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>745.0410185589892</v>
+        <v>745.041018558989</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>8222822.995881463</v>
+        <v>8222822.995881461</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>9947157.719984176</v>
+        <v>9947157.719984172</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>11664102.01864643</v>
+        <v>11664102.01864642</v>
       </c>
       <c r="AG39" s="165" t="n">
         <v>13612802.59091012</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>2426.569050717375</v>
+        <v>2426.569050717374</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>2552.346064419263</v>
+        <v>2552.346064419262</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>2682.726579747777</v>
+        <v>2682.726579747775</v>
       </c>
       <c r="F40" s="156" t="n">
         <v>2831.134549650115</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>2990.089602021657</v>
+        <v>2990.089602021656</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2426.569050717375</v>
+        <v>2426.569050717374</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>2552.346064419263</v>
+        <v>2552.346064419262</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>2682.726579747777</v>
+        <v>2682.726579747775</v>
       </c>
       <c r="K40" s="156" t="n">
         <v>2831.134549650115</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>2990.089602021657</v>
+        <v>2990.089602021656</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>3096781.174902076</v>
+        <v>3096781.174902074</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>3700082.225650087</v>
+        <v>3700082.225650085</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>4374951.674573726</v>
+        <v>4374951.674573724</v>
       </c>
       <c r="P40" s="159" t="n">
         <v>5209968.64323729</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>6246890.791323047</v>
+        <v>6246890.791323044</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,13 +4968,13 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>1290.432062667656</v>
+        <v>1290.432062667655</v>
       </c>
       <c r="U40" s="156" t="n">
         <v>1357.319378806268</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>1426.654804178691</v>
+        <v>1426.65480417869</v>
       </c>
       <c r="W40" s="156" t="n">
         <v>1505.577100933765</v>
@@ -4983,13 +4983,13 @@
         <v>1590.108260697223</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>1290.432062667656</v>
+        <v>1290.432062667655</v>
       </c>
       <c r="Z40" s="156" t="n">
         <v>1357.319378806268</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1426.654804178691</v>
+        <v>1426.65480417869</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>1505.577100933765</v>
@@ -4998,19 +4998,19 @@
         <v>1590.108260697223</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>3096781.174902076</v>
+        <v>3096781.174902074</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>3700082.225650087</v>
+        <v>3700082.225650085</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>4374951.674573726</v>
+        <v>4374951.674573724</v>
       </c>
       <c r="AG40" s="159" t="n">
         <v>5209968.64323729</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>6246890.791323047</v>
+        <v>6246890.791323044</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>627.6417997140932</v>
+        <v>627.6417997140927</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>686.943240229733</v>
+        <v>686.9432402297326</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>739.3004008934402</v>
+        <v>739.3004008934398</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>858.8990162319905</v>
+        <v>858.8990162319902</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>922.1444054643829</v>
+        <v>922.1444054643825</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>627.6417997140932</v>
+        <v>627.6417997140927</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>686.943240229733</v>
+        <v>686.9432402297326</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>739.3004008934402</v>
+        <v>739.3004008934398</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>858.8990162319905</v>
+        <v>858.8990162319902</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>922.1444054643829</v>
+        <v>922.1444054643825</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>11319604.17078354</v>
+        <v>11319604.17078353</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>13647239.94563426</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>16039053.69322016</v>
+        <v>16039053.69322015</v>
       </c>
       <c r="P41" s="183" t="n">
         <v>18822771.23414741</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>22231512.29120949</v>
+        <v>22231512.29120948</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>607.0020542166096</v>
+        <v>607.0020542166092</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>662.6234197898357</v>
+        <v>662.6234197898355</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>711.5156604731011</v>
+        <v>711.5156604731009</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>817.6072758964914</v>
+        <v>817.607275896491</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>875.8328818013446</v>
+        <v>875.8328818013441</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>607.0020542166096</v>
+        <v>607.0020542166092</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>662.6234197898357</v>
+        <v>662.6234197898355</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>711.5156604731011</v>
+        <v>711.5156604731009</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>817.6072758964914</v>
+        <v>817.607275896491</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>875.8328818013446</v>
+        <v>875.8328818013441</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>11319604.17078354</v>
+        <v>11319604.17078353</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>13647239.94563426</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>16039053.69322016</v>
+        <v>16039053.69322015</v>
       </c>
       <c r="AG41" s="189" t="n">
         <v>18822771.23414741</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>22231512.29120949</v>
+        <v>22231512.29120948</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3146440548149475</v>
+        <v>0.3146440548149472</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.1969582933994464</v>
+        <v>0.1969582933994462</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.140021465799307</v>
+        <v>0.1400214657993071</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0969958653124911</v>
+        <v>0.09699586531249099</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.05181273658821457</v>
+        <v>0.05181273658821452</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.3146440548149475</v>
+        <v>0.3146440548149472</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.1969582933994464</v>
+        <v>0.1969582933994462</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.140021465799307</v>
+        <v>0.1400214657993071</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.0969958653124911</v>
+        <v>0.09699586531249099</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.05181273658821457</v>
+        <v>0.05181273658821452</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>4352.346691058558</v>
+        <v>4352.346691058555</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3007.862467254743</v>
+        <v>3007.862467254739</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2334.622199141254</v>
+        <v>2334.622199141255</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1655.104930299171</v>
+        <v>1655.104930299169</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>969.1271590179583</v>
+        <v>969.1271590179574</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.3138395885571764</v>
+        <v>0.3138395885571761</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1964547202385894</v>
+        <v>0.1964547202385892</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0.1396634658851964</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.09674787111208233</v>
+        <v>0.09674787111208222</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.0516802643623131</v>
+        <v>0.05168026436231305</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.3138395885571764</v>
+        <v>0.3138395885571761</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.1964547202385894</v>
+        <v>0.1964547202385892</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0.1396634658851964</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.09674787111208233</v>
+        <v>0.09674787111208222</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.0516802643623131</v>
+        <v>0.05168026436231305</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>4352.346691058558</v>
+        <v>4352.346691058555</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3007.862467254743</v>
+        <v>3007.862467254739</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2334.622199141254</v>
+        <v>2334.622199141255</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1655.104930299171</v>
+        <v>1655.104930299169</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>969.1271590179583</v>
+        <v>969.1271590179574</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3115754436703134</v>
+        <v>0.3115754436703131</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.1404911508317169</v>
+        <v>0.140491150831717</v>
       </c>
       <c r="E58" s="156" t="n">
         <v>0.1015573505611832</v>
@@ -6448,13 +6448,13 @@
         <v>0.08141768103264786</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.04349887486115507</v>
+        <v>0.04349887486115506</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.3115754436703134</v>
+        <v>0.3115754436703131</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.1404911508317169</v>
+        <v>0.140491150831717</v>
       </c>
       <c r="J58" s="156" t="n">
         <v>0.1015573505611832</v>
@@ -6463,16 +6463,16 @@
         <v>0.08141768103264786</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.04349887486115507</v>
+        <v>0.04349887486115506</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>887.0879937329344</v>
+        <v>887.0879937329336</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>429.6485596328099</v>
+        <v>429.6485596328102</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>334.3595724170734</v>
+        <v>334.3595724170735</v>
       </c>
       <c r="P58" s="159" t="n">
         <v>236.3234559141056</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3851342870941586</v>
+        <v>0.3851342870941583</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.1736592543405453</v>
+        <v>0.1736592543405454</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0.1255336985059055</v>
@@ -6498,13 +6498,13 @@
         <v>0.1006393192351445</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.0537683841887607</v>
+        <v>0.05376838418876068</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.3851342870941586</v>
+        <v>0.3851342870941583</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.1736592543405453</v>
+        <v>0.1736592543405454</v>
       </c>
       <c r="AA58" s="156" t="n">
         <v>0.1255336985059055</v>
@@ -6513,16 +6513,16 @@
         <v>0.1006393192351445</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.0537683841887607</v>
+        <v>0.05376838418876068</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>887.0879937329344</v>
+        <v>887.0879937329336</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>429.6485596328099</v>
+        <v>429.6485596328102</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>334.3595724170734</v>
+        <v>334.3595724170735</v>
       </c>
       <c r="AG58" s="159" t="n">
         <v>236.3234559141056</v>
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.3141202652260627</v>
+        <v>0.3141202652260624</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1875371541481166</v>
+        <v>0.1875371541481164</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.1336787547142617</v>
+        <v>0.1336787547142618</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.09473117939683996</v>
+        <v>0.09473117939683987</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.0506012695174459</v>
+        <v>0.05060126951744586</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.3141202652260627</v>
+        <v>0.3141202652260624</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.1875371541481166</v>
+        <v>0.1875371541481164</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.1336787547142617</v>
+        <v>0.1336787547142618</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.09473117939683996</v>
+        <v>0.09473117939683987</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.0506012695174459</v>
+        <v>0.05060126951744586</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>5239.434684791493</v>
+        <v>5239.434684791489</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>3437.511026887552</v>
+        <v>3437.511026887549</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>2668.981771558328</v>
+        <v>2668.981771558329</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>1891.428386213277</v>
+        <v>1891.428386213275</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1107.907857899868</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.3239942301516885</v>
+        <v>0.3239942301516883</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.1932835849302449</v>
+        <v>0.1932835849302447</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0.1377214868198834</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.09721755447120013</v>
+        <v>0.09721755447120005</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.05193290106398935</v>
+        <v>0.05193290106398931</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.3239942301516885</v>
+        <v>0.3239942301516883</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.1932835849302449</v>
+        <v>0.1932835849302447</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0.1377214868198834</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.09721755447120013</v>
+        <v>0.09721755447120005</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.05193290106398935</v>
+        <v>0.05193290106398931</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>5239.434684791493</v>
+        <v>5239.434684791489</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>3437.511026887552</v>
+        <v>3437.511026887549</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>2668.981771558328</v>
+        <v>2668.981771558329</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>1891.428386213277</v>
+        <v>1891.428386213275</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1107.907857899868</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.382788901847193</v>
+        <v>0.3827889018471928</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.382788901847193</v>
+        <v>0.3827889018471928</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>30.32747865321118</v>
+        <v>30.32747865321117</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.3928724674319574</v>
+        <v>0.3928724674319573</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.3928724674319574</v>
+        <v>0.3928724674319573</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>30.32747865321118</v>
+        <v>30.32747865321117</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.3144448954315729</v>
+        <v>0.3144448954315726</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.1866494065410075</v>
+        <v>0.1866494065410074</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.133022606038399</v>
+        <v>0.1330226060383991</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0942192343498456</v>
+        <v>0.09421923434984551</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.05031531960783869</v>
+        <v>0.05031531960783865</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.3144448954315729</v>
+        <v>0.3144448954315726</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.1866494065410075</v>
+        <v>0.1866494065410074</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.133022606038399</v>
+        <v>0.1330226060383991</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.0942192343498456</v>
+        <v>0.09421923434984551</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.05031531960783869</v>
+        <v>0.05031531960783865</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>5269.762163444704</v>
+        <v>5269.7621634447</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>3437.511026887552</v>
+        <v>3437.511026887549</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>2668.981771558328</v>
+        <v>2668.981771558329</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>1891.428386213277</v>
+        <v>1891.428386213275</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1107.907857899868</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.3243214588655637</v>
+        <v>0.3243214588655634</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.1923648209854664</v>
+        <v>0.1923648209854662</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.1370429389003477</v>
+        <v>0.1370429389003478</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.09669222132520446</v>
+        <v>0.09669222132520437</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.0516394334970703</v>
+        <v>0.05163943349707026</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.3243214588655637</v>
+        <v>0.3243214588655634</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.1923648209854664</v>
+        <v>0.1923648209854662</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.1370429389003477</v>
+        <v>0.1370429389003478</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.09669222132520446</v>
+        <v>0.09669222132520437</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.0516394334970703</v>
+        <v>0.05163943349707026</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>5269.762163444704</v>
+        <v>5269.7621634447</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>3437.511026887552</v>
+        <v>3437.511026887549</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>2668.981771558328</v>
+        <v>2668.981771558329</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>1891.428386213277</v>
+        <v>1891.428386213275</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1107.907857899868</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.2921942285637998</v>
+        <v>0.2921942285637995</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.173029489665489</v>
+        <v>0.1730294896654888</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.1230234234158363</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.08630748150647803</v>
+        <v>0.08630748150647796</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.04595508481608608</v>
+        <v>0.04595508481608605</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.2921942285637998</v>
+        <v>0.2921942285637995</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.173029489665489</v>
+        <v>0.1730294896654888</v>
       </c>
       <c r="J63" s="180" t="n">
         <v>0.1230234234158363</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.08630748150647803</v>
+        <v>0.08630748150647796</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.04595508481608608</v>
+        <v>0.04595508481608605</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>5269.762163444704</v>
+        <v>5269.7621634447</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>3437.511026887552</v>
+        <v>3437.511026887549</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>2668.981771558328</v>
+        <v>2668.981771558329</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>1891.428386213277</v>
+        <v>1891.428386213275</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>1107.907857899869</v>
+        <v>1107.907857899868</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.2825855401110269</v>
+        <v>0.2825855401110267</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.1669037344749081</v>
+        <v>0.1669037344749079</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.1183998984169324</v>
+        <v>0.1183998984169325</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.08215823223732555</v>
+        <v>0.08215823223732546</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.04364714911178027</v>
+        <v>0.04364714911178023</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.2825855401110269</v>
+        <v>0.2825855401110267</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.1669037344749081</v>
+        <v>0.1669037344749079</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.1183998984169324</v>
+        <v>0.1183998984169325</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.08215823223732555</v>
+        <v>0.08215823223732546</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.04364714911178027</v>
+        <v>0.04364714911178023</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>5269.762163444704</v>
+        <v>5269.7621634447</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>3437.511026887552</v>
+        <v>3437.511026887549</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>2668.981771558328</v>
+        <v>2668.981771558329</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>1891.428386213277</v>
+        <v>1891.428386213275</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>1107.907857899869</v>
+        <v>1107.907857899868</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>2.555161381276752</v>
+        <v>2.55516138127675</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>3.13304784452606</v>
+        <v>3.133047844526056</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>3.590343883132825</v>
+        <v>3.590343883132826</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.77511812783606</v>
+        <v>1.775118127836058</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>1.784111356110195</v>
+        <v>1.784111356110193</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>2.555161381276752</v>
+        <v>2.55516138127675</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>3.13304784452606</v>
+        <v>3.133047844526056</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>3.590343883132825</v>
+        <v>3.590343883132826</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>1.77511812783606</v>
+        <v>1.775118127836058</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>1.784111356110195</v>
+        <v>1.784111356110193</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>35344.53619173286</v>
+        <v>35344.53619173283</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>47846.5611019038</v>
+        <v>47846.56110190374</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>59862.93947334459</v>
+        <v>59862.9394733446</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>30290.02067025781</v>
+        <v>30290.02067025777</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>33370.76718530322</v>
+        <v>33370.76718530318</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>2.548628471841658</v>
+        <v>2.548628471841656</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>3.125037423746345</v>
+        <v>3.125037423746341</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>3.58116427060376</v>
+        <v>3.581164270603761</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>1.770579594164284</v>
+        <v>1.770579594164281</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>1.77954982900001</v>
+        <v>1.779549829000008</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>2.548628471841658</v>
+        <v>2.548628471841656</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>3.125037423746345</v>
+        <v>3.125037423746341</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>3.58116427060376</v>
+        <v>3.581164270603761</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>1.770579594164284</v>
+        <v>1.770579594164281</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>1.77954982900001</v>
+        <v>1.779549829000008</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>35344.53619173286</v>
+        <v>35344.53619173283</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>47846.5611019038</v>
+        <v>47846.56110190374</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>59862.93947334459</v>
+        <v>59862.9394733446</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>30290.02067025781</v>
+        <v>30290.02067025777</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>33370.76718530322</v>
+        <v>33370.76718530318</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>10.63919364653762</v>
+        <v>10.63919364653761</v>
       </c>
       <c r="D69" s="156" t="n">
         <v>13.86655829695429</v>
@@ -7411,10 +7411,10 @@
         <v>3.884095473578154</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.184874492837191</v>
+        <v>4.18487449283719</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>10.63919364653762</v>
+        <v>10.63919364653761</v>
       </c>
       <c r="I69" s="156" t="n">
         <v>13.86655829695429</v>
@@ -7426,13 +7426,13 @@
         <v>3.884095473578154</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.184874492837191</v>
+        <v>4.18487449283719</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>30290.90109177456</v>
+        <v>30290.90109177453</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>42406.56272000439</v>
+        <v>42406.5627200044</v>
       </c>
       <c r="O69" s="159" t="n">
         <v>54873.83669288546</v>
@@ -7441,7 +7441,7 @@
         <v>11273.99913353283</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>13351.60527031627</v>
+        <v>13351.60527031626</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>13.15096662319661</v>
+        <v>13.1509666231966</v>
       </c>
       <c r="U69" s="156" t="n">
         <v>17.14026940389435</v>
@@ -7461,10 +7461,10 @@
         <v>4.801079069649091</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>5.172868039250249</v>
+        <v>5.172868039250248</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>13.15096662319661</v>
+        <v>13.1509666231966</v>
       </c>
       <c r="Z69" s="156" t="n">
         <v>17.14026940389435</v>
@@ -7476,13 +7476,13 @@
         <v>4.801079069649091</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>5.172868039250249</v>
+        <v>5.172868039250248</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>30290.90109177456</v>
+        <v>30290.90109177453</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>42406.56272000439</v>
+        <v>42406.5627200044</v>
       </c>
       <c r="AF69" s="159" t="n">
         <v>54873.83669288546</v>
@@ -7491,7 +7491,7 @@
         <v>11273.99913353283</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>13351.60527031627</v>
+        <v>13351.60527031626</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>3.935046852968726</v>
+        <v>3.935046852968722</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>4.923857367190323</v>
+        <v>4.923857367190321</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>5.746711918858614</v>
+        <v>5.746711918858615</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.081711708033295</v>
+        <v>2.081711708033293</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.133942226570043</v>
+        <v>2.133942226570041</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>3.935046852968726</v>
+        <v>3.935046852968722</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>4.923857367190323</v>
+        <v>4.923857367190321</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>5.746711918858614</v>
+        <v>5.746711918858615</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>2.081711708033295</v>
+        <v>2.081711708033293</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>2.133942226570043</v>
+        <v>2.133942226570041</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>65635.43728350742</v>
+        <v>65635.43728350736</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>90253.12382190819</v>
+        <v>90253.12382190814</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>114736.77616623</v>
+        <v>114736.7761662301</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>41564.01980379064</v>
+        <v>41564.01980379059</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>46722.37245561949</v>
+        <v>46722.37245561944</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>4.058739969612904</v>
+        <v>4.0587399696129</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>5.074732033440642</v>
+        <v>5.07473203344064</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>5.920504806335666</v>
+        <v>5.920504806335667</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.136349643883067</v>
+        <v>2.136349643883065</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.190099410263273</v>
+        <v>2.19009941026327</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>4.058739969612904</v>
+        <v>4.0587399696129</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>5.074732033440642</v>
+        <v>5.07473203344064</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>5.920504806335666</v>
+        <v>5.920504806335667</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>2.136349643883067</v>
+        <v>2.136349643883065</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>2.190099410263273</v>
+        <v>2.19009941026327</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>65635.43728350742</v>
+        <v>65635.43728350736</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>90253.12382190819</v>
+        <v>90253.12382190814</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>114736.77616623</v>
+        <v>114736.7761662301</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>41564.01980379064</v>
+        <v>41564.01980379059</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>46722.37245561949</v>
+        <v>46722.37245561944</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,46 +7603,46 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>7.85590233887873</v>
+        <v>7.855902338878728</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>9.493191150191411</v>
+        <v>9.493191150191414</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>10.77537937205628</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>9.162110620338812</v>
+        <v>9.162110620338813</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>9.732353498064471</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>7.85590233887873</v>
+        <v>7.855902338878728</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>9.493191150191411</v>
+        <v>9.493191150191414</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>10.77537937205628</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>9.162110620338812</v>
+        <v>9.162110620338813</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>9.732353498064471</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>622.4049582794967</v>
+        <v>622.4049582794964</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>827.6217610569504</v>
+        <v>827.6217610569507</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>1061.188636549175</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>993.9768374021296</v>
+        <v>993.9768374021297</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>1211.015864900466</v>
@@ -7653,46 +7653,46 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>8.062845398302146</v>
+        <v>8.062845398302144</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>9.743264271720607</v>
+        <v>9.74326427172061</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>11.05922836578239</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>9.403462297174871</v>
+        <v>9.403462297174872</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>9.988726721839441</v>
+        <v>9.98872672183944</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>8.062845398302146</v>
+        <v>8.062845398302144</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>9.743264271720607</v>
+        <v>9.74326427172061</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>11.05922836578239</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>9.403462297174871</v>
+        <v>9.403462297174872</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>9.988726721839441</v>
+        <v>9.98872672183944</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>622.4049582794967</v>
+        <v>622.4049582794964</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>827.6217610569504</v>
+        <v>827.6217610569507</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>1061.188636549175</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>993.9768374021296</v>
+        <v>993.9768374021297</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>1211.015864900466</v>
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>3.953582653077729</v>
+        <v>3.953582653077724</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>4.945487295139095</v>
+        <v>4.945487295139093</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>5.771394625529711</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.119975510690227</v>
+        <v>2.119975510690225</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.176881169346826</v>
+        <v>2.176881169346824</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>3.953582653077729</v>
+        <v>3.953582653077724</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>4.945487295139095</v>
+        <v>4.945487295139093</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>5.771394625529711</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>2.119975510690227</v>
+        <v>2.119975510690225</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>2.176881169346826</v>
+        <v>2.176881169346824</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>66257.84224178692</v>
+        <v>66257.84224178686</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>91080.74558296513</v>
+        <v>91080.74558296509</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>115797.9648027792</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>42557.99664119277</v>
+        <v>42557.99664119272</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>47933.38832051995</v>
+        <v>47933.38832051991</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>4.077762789031453</v>
+        <v>4.07776278903145</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>5.096923670134029</v>
+        <v>5.096923670134026</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>5.945823079183619</v>
+        <v>5.94582307918362</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.175618839382011</v>
+        <v>2.175618839382009</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.234168663772079</v>
+        <v>2.234168663772077</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>4.077762789031453</v>
+        <v>4.07776278903145</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>5.096923670134029</v>
+        <v>5.096923670134026</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>5.945823079183619</v>
+        <v>5.94582307918362</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.175618839382011</v>
+        <v>2.175618839382009</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>2.234168663772079</v>
+        <v>2.234168663772077</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>66257.84224178692</v>
+        <v>66257.84224178686</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>91080.74558296513</v>
+        <v>91080.74558296509</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>115797.9648027792</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>42557.99664119277</v>
+        <v>42557.99664119272</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>47933.38832051995</v>
+        <v>47933.38832051991</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7810,46 +7810,46 @@
         <v>21.26525340015822</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>26.64197220776436</v>
+        <v>26.64197220776435</v>
       </c>
       <c r="E73" s="156" t="n">
         <v>33.52184395119495</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>41.6772902462374</v>
+        <v>41.67729024623737</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>50.90141856033816</v>
+        <v>50.90141856033814</v>
       </c>
       <c r="H73" s="155" t="n">
         <v>21.26525340015822</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>26.64197220776436</v>
+        <v>26.64197220776435</v>
       </c>
       <c r="J73" s="156" t="n">
         <v>33.52184395119495</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>41.6772902462374</v>
+        <v>41.67729024623737</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>50.90141856033816</v>
+        <v>50.90141856033814</v>
       </c>
       <c r="M73" s="158" t="n">
         <v>27138.66163819395</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>38622.30486548145</v>
+        <v>38622.30486548143</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>54666.93789676759</v>
+        <v>54666.9378967676</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>76696.24015037755</v>
+        <v>76696.24015037747</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>106343.1686645334</v>
+        <v>106343.1686645333</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7860,46 +7860,46 @@
         <v>11.30870963684465</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>14.16801023627824</v>
+        <v>14.16801023627823</v>
       </c>
       <c r="V73" s="156" t="n">
         <v>17.82667681415263</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>22.16368481372951</v>
+        <v>22.16368481372949</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>27.06901026620621</v>
+        <v>27.0690102662062</v>
       </c>
       <c r="Y73" s="155" t="n">
         <v>11.30870963684465</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>14.16801023627824</v>
+        <v>14.16801023627823</v>
       </c>
       <c r="AA73" s="156" t="n">
         <v>17.82667681415263</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>22.16368481372951</v>
+        <v>22.16368481372949</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>27.06901026620621</v>
+        <v>27.0690102662062</v>
       </c>
       <c r="AD73" s="158" t="n">
         <v>27138.66163819395</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>38622.30486548145</v>
+        <v>38622.30486548143</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>54666.93789676759</v>
+        <v>54666.9378967676</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>76696.24015037755</v>
+        <v>76696.24015037747</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>106343.1686645334</v>
+        <v>106343.1686645333</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>5.178586538700306</v>
+        <v>5.178586538700301</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>6.528692548652591</v>
+        <v>6.528692548652588</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>7.857369475439063</v>
+        <v>7.857369475439064</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>5.441671972082281</v>
+        <v>5.441671972082276</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>6.399261645116546</v>
+        <v>6.399261645116543</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>5.178586538700306</v>
+        <v>5.178586538700301</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>6.528692548652591</v>
+        <v>6.528692548652588</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>7.857369475439063</v>
+        <v>7.857369475439064</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>5.441671972082281</v>
+        <v>5.441671972082276</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>6.399261645116546</v>
+        <v>6.399261645116543</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>93396.50387998087</v>
+        <v>93396.5038799808</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>129703.0504484466</v>
+        <v>129703.0504484465</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>170464.9026995468</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>119254.2367915703</v>
+        <v>119254.2367915702</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>154276.5569850533</v>
+        <v>154276.5569850532</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>5.008290825055743</v>
+        <v>5.008290825055739</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>6.297557541868876</v>
+        <v>6.297557541868874</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>7.562070066703537</v>
+        <v>7.562070066703539</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>5.180062514141659</v>
+        <v>5.180062514141653</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>6.077880790504579</v>
+        <v>6.077880790504575</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>5.008290825055743</v>
+        <v>5.008290825055739</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>6.297557541868876</v>
+        <v>6.297557541868874</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>7.562070066703537</v>
+        <v>7.562070066703539</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>5.180062514141659</v>
+        <v>5.180062514141653</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>6.077880790504579</v>
+        <v>6.077880790504575</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>93396.50387998087</v>
+        <v>93396.5038799808</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>129703.0504484466</v>
+        <v>129703.0504484465</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>170464.9026995468</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>119254.2367915703</v>
+        <v>119254.2367915702</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>154276.5569850533</v>
+        <v>154276.5569850532</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,46 +8260,46 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>421.0039999652952</v>
+        <v>421.003999965295</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>462.4771255086719</v>
+        <v>462.4771255086717</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>497.4923347691824</v>
+        <v>497.4923347691822</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>568.2988410882807</v>
+        <v>568.2988410882805</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>608.3664005904088</v>
+        <v>608.3664005904085</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>421.0039999652952</v>
+        <v>421.003999965295</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>462.4771255086719</v>
+        <v>462.4771255086717</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>497.4923347691824</v>
+        <v>497.4923347691822</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>568.2988410882807</v>
+        <v>568.2988410882805</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>608.3664005904088</v>
+        <v>608.3664005904085</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>5823581.720776635</v>
+        <v>5823581.720776632</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>7062752.03634205</v>
+        <v>7062752.036342047</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>8294847.093798198</v>
+        <v>8294847.093798194</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>9697260.916619599</v>
+        <v>9697260.916619595</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>11379140.34790187</v>
@@ -8310,46 +8310,46 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>419.927597893888</v>
+        <v>419.9275978938879</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>461.294687014223</v>
+        <v>461.2946870142228</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>496.2203711305974</v>
+        <v>496.2203711305972</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>566.8458428987716</v>
+        <v>566.8458428987714</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>606.8109596591493</v>
+        <v>606.810959659149</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>419.927597893888</v>
+        <v>419.9275978938879</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>461.294687014223</v>
+        <v>461.2946870142228</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>496.2203711305974</v>
+        <v>496.2203711305972</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>566.8458428987716</v>
+        <v>566.8458428987714</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>606.8109596591493</v>
+        <v>606.810959659149</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>5823581.720776635</v>
+        <v>5823581.720776632</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>7062752.03634205</v>
+        <v>7062752.036342047</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>8294847.093798198</v>
+        <v>8294847.093798194</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>9697260.916619599</v>
+        <v>9697260.916619595</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>11379140.34790187</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>835.8044764048716</v>
+        <v>835.8044764048714</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>937.4017868567873</v>
@@ -8377,7 +8377,7 @@
         <v>1396.675752547503</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>835.8044764048716</v>
+        <v>835.8044764048715</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>937.4017868567873</v>
@@ -8398,7 +8398,7 @@
         <v>2866752.283940409</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>3351931.728367888</v>
+        <v>3351931.728367887</v>
       </c>
       <c r="P80" s="159" t="n">
         <v>3796488.658781372</v>
@@ -8448,7 +8448,7 @@
         <v>2866752.283940409</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>3351931.728367888</v>
+        <v>3351931.728367887</v>
       </c>
       <c r="AG80" s="159" t="n">
         <v>3796488.658781372</v>
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>491.8074223550757</v>
+        <v>491.8074223550756</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>541.7149116793554</v>
+        <v>541.7149116793553</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>583.3411475382845</v>
+        <v>583.3411475382844</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>675.8272325194998</v>
+        <v>675.8272325194996</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>723.2361028813052</v>
+        <v>723.236102881305</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>491.8074223550757</v>
+        <v>491.8074223550756</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>541.7149116793554</v>
+        <v>541.7149116793553</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>583.3411475382845</v>
+        <v>583.3411475382844</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>675.8272325194998</v>
+        <v>675.8272325194996</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>723.2361028813052</v>
+        <v>723.236102881305</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>8203204.798234347</v>
+        <v>8203204.798234344</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>9929504.320282459</v>
+        <v>9929504.320282456</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>11646778.82216609</v>
+        <v>11646778.82216608</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>13493749.57540097</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>15835155.30618886</v>
+        <v>15835155.30618885</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>507.2667536242688</v>
+        <v>507.2667536242686</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>558.3139011316193</v>
+        <v>558.3139011316191</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>600.9826343304381</v>
+        <v>600.9826343304379</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>693.5654259655148</v>
+        <v>693.5654259655147</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>742.2689061959304</v>
+        <v>742.2689061959302</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>507.2667536242688</v>
+        <v>507.2667536242686</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>558.3139011316193</v>
+        <v>558.3139011316191</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>600.9826343304381</v>
+        <v>600.9826343304379</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>693.5654259655148</v>
+        <v>693.5654259655147</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>742.2689061959304</v>
+        <v>742.2689061959302</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>8203204.798234347</v>
+        <v>8203204.798234344</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>9929504.320282459</v>
+        <v>9929504.320282456</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>11646778.82216609</v>
+        <v>11646778.82216608</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>13493749.57540097</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>15835155.30618886</v>
+        <v>15835155.30618885</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8596,7 +8596,7 @@
         <v>1595.309458349266</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>91145.80205234843</v>
+        <v>91145.80205234844</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>112171.6563115685</v>
@@ -8622,7 +8622,7 @@
         <v>1320.552627621185</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1415.143500544243</v>
+        <v>1415.143500544244</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>1546.805697303743</v>
@@ -8637,7 +8637,7 @@
         <v>1320.552627621185</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1415.143500544243</v>
+        <v>1415.143500544244</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>1546.805697303743</v>
@@ -8646,7 +8646,7 @@
         <v>1637.333684949445</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>91145.80205234843</v>
+        <v>91145.80205234844</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>112171.6563115685</v>
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>494.9210469633601</v>
+        <v>494.9210469633598</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>545.2412652783262</v>
+        <v>545.2412652783261</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>587.2456853332901</v>
+        <v>587.24568533329</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>680.3196132848049</v>
+        <v>680.3196132848046</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>728.1642262178341</v>
+        <v>728.1642262178339</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>494.9210469633601</v>
+        <v>494.9210469633598</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>545.2412652783262</v>
+        <v>545.2412652783261</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>587.2456853332901</v>
+        <v>587.24568533329</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>680.3196132848049</v>
+        <v>680.3196132848046</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>728.1642262178341</v>
+        <v>728.1642262178339</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>8294350.600286696</v>
+        <v>8294350.600286693</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>10041675.97659403</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>11782568.96522077</v>
+        <v>11782568.96522076</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>13657252.01593753</v>
+        <v>13657252.01593752</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>16033662.79606486</v>
+        <v>16033662.79606485</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>510.4662798043698</v>
+        <v>510.4662798043696</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>561.9371651530581</v>
+        <v>561.9371651530579</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>604.9939703586299</v>
+        <v>604.9939703586298</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>698.1760685441152</v>
+        <v>698.1760685441151</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>747.3268266562582</v>
+        <v>747.3268266562579</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>510.4662798043698</v>
+        <v>510.4662798043696</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>561.9371651530581</v>
+        <v>561.9371651530579</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>604.9939703586299</v>
+        <v>604.9939703586298</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>698.1760685441152</v>
+        <v>698.1760685441151</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>747.3268266562582</v>
+        <v>747.3268266562579</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>8294350.600286696</v>
+        <v>8294350.600286693</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>10041675.97659403</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>11782568.96522077</v>
+        <v>11782568.96522076</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>13657252.01593753</v>
+        <v>13657252.01593752</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>16033662.79606486</v>
+        <v>16033662.79606485</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>2447.834304117533</v>
+        <v>2447.834304117532</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>2578.988036627027</v>
+        <v>2578.988036627026</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>2716.248423698972</v>
+        <v>2716.24842369897</v>
       </c>
       <c r="F84" s="156" t="n">
         <v>2872.811839896353</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3040.991020581995</v>
+        <v>3040.991020581994</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2447.834304117533</v>
+        <v>2447.834304117532</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>2578.988036627027</v>
+        <v>2578.988036627026</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>2716.248423698972</v>
+        <v>2716.24842369897</v>
       </c>
       <c r="K84" s="156" t="n">
         <v>2872.811839896352</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3040.991020581995</v>
+        <v>3040.991020581994</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>3123919.83654027</v>
+        <v>3123919.836540268</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>3738704.530515568</v>
+        <v>3738704.530515566</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>4429618.612470494</v>
+        <v>4429618.612470492</v>
       </c>
       <c r="P84" s="159" t="n">
         <v>5286664.883387667</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>6353233.959987581</v>
+        <v>6353233.959987578</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>1301.740772304501</v>
+        <v>1301.7407723045</v>
       </c>
       <c r="U84" s="156" t="n">
         <v>1371.487389042546</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>1444.481480992844</v>
+        <v>1444.481480992843</v>
       </c>
       <c r="W84" s="156" t="n">
         <v>1527.740785747495</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>1617.17727096343</v>
+        <v>1617.177270963429</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>1301.740772304501</v>
+        <v>1301.7407723045</v>
       </c>
       <c r="Z84" s="156" t="n">
         <v>1371.487389042546</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1444.481480992844</v>
+        <v>1444.481480992843</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>1527.740785747495</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1617.17727096343</v>
+        <v>1617.177270963429</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>3123919.83654027</v>
+        <v>3123919.836540268</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>3738704.530515568</v>
+        <v>3738704.530515566</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>4429618.612470494</v>
+        <v>4429618.612470492</v>
       </c>
       <c r="AG84" s="159" t="n">
         <v>5286664.883387667</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>6353233.959987581</v>
+        <v>6353233.959987578</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>633.1125804813573</v>
+        <v>633.1125804813568</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>693.6449622680509</v>
+        <v>693.6449622680506</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>747.280793792295</v>
+        <v>747.2807937922947</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>864.426995685579</v>
+        <v>864.4269956855788</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>928.5896221943153</v>
+        <v>928.589622194315</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>633.1125804813573</v>
+        <v>633.1125804813568</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>693.6449622680509</v>
+        <v>693.6449622680506</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>747.280793792295</v>
+        <v>747.2807937922947</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>864.426995685579</v>
+        <v>864.4269956855788</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>928.5896221943153</v>
+        <v>928.589622194315</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>11418270.43682697</v>
+        <v>11418270.43682696</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>13780380.50710959</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>16212187.57769126</v>
+        <v>16212187.57769125</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>18943916.89932519</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>22386896.75605244</v>
+        <v>22386896.75605243</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>612.2929305817764</v>
+        <v>612.2929305817759</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>669.0878810661793</v>
+        <v>669.0878810661791</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>719.1961304382214</v>
+        <v>719.1961304382213</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>822.8694966428701</v>
+        <v>822.8694966428699</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>881.9544097409607</v>
+        <v>881.9544097409603</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>612.2929305817764</v>
+        <v>612.2929305817759</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>669.0878810661793</v>
+        <v>669.0878810661791</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>719.1961304382214</v>
+        <v>719.1961304382213</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>822.8694966428701</v>
+        <v>822.8694966428699</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>881.9544097409607</v>
+        <v>881.9544097409603</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>11418270.43682697</v>
+        <v>11418270.43682696</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>13780380.50710959</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>16212187.57769126</v>
+        <v>16212187.57769125</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>18943916.89932519</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>22386896.75605244</v>
+        <v>22386896.75605243</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>79.22768530347238</v>
+        <v>79.22768530347237</v>
       </c>
       <c r="D93" s="80" t="n">
         <v>87.18056425528344</v>
@@ -9666,7 +9666,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="79" t="n">
-        <v>79.22768530347238</v>
+        <v>79.22768530347237</v>
       </c>
       <c r="N93" s="80" t="n">
         <v>87.18056425528344</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>77.19420719769241</v>
+        <v>77.19420719769239</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>84.94296551711996</v>
@@ -9716,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="AD93" s="79" t="n">
-        <v>77.19420719769241</v>
+        <v>77.19420719769239</v>
       </c>
       <c r="AE93" s="80" t="n">
         <v>84.94296551711996</v>
@@ -9809,7 +9809,7 @@
         <v>16248.5768961378</v>
       </c>
       <c r="U94" s="86" t="n">
-        <v>17869.74878918876</v>
+        <v>17869.74878918877</v>
       </c>
       <c r="V94" s="86" t="n">
         <v>19475.51470345442</v>
@@ -9839,7 +9839,7 @@
         <v>16248.5768961378</v>
       </c>
       <c r="AE94" s="86" t="n">
-        <v>17869.74878918876</v>
+        <v>17869.74878918877</v>
       </c>
       <c r="AF94" s="86" t="n">
         <v>19475.51470345442</v>
@@ -9874,7 +9874,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="E95" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="F95" s="80" t="n">
         <v>1840.240564999343</v>
@@ -9904,7 +9904,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="O95" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="P95" s="80" t="n">
         <v>1840.240564999343</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>18648.37868694283</v>
+        <v>18648.37868694284</v>
       </c>
       <c r="U96" s="136" t="n">
         <v>20595.77059615967</v>
@@ -10068,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>18648.37868694283</v>
+        <v>18648.37868694284</v>
       </c>
       <c r="AE96" s="136" t="n">
         <v>20595.77059615967</v>
